--- a/AAII_Financials/Yearly/HNTIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HNTIY_YR_FIN.xlsx
@@ -3148,7 +3148,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-45100</v>
+        <v>-26900</v>
       </c>
       <c r="E91" s="3">
         <v>-23600</v>
